--- a/data/trans_orig/IP07C04-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07C04-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse  alegre en 2007 (tasa de respuesta: 89,79%)</t>
+          <t>Menores según la frecuencia de sentirse alegre en 2007 (tasa de respuesta: 89,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>63479</t>
+          <t>63082</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>80283</t>
+          <t>79714</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>56,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>71,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>70746</t>
+          <t>70068</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>87606</t>
+          <t>87665</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>70,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>139218</t>
+          <t>139988</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>163085</t>
+          <t>163904</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,34%</t>
+          <t>69,69%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27021</t>
+          <t>27521</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43674</t>
+          <t>44013</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30797</t>
+          <t>30470</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>46843</t>
+          <t>47627</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>62161</t>
+          <t>61950</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>84983</t>
+          <t>84146</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>35,78%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7645</t>
+          <t>7999</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2469</t>
+          <t>1923</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9841</t>
+          <t>9377</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4730</t>
+          <t>4796</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13766</t>
+          <t>14271</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,07%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3590</t>
+          <t>4030</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4375</t>
+          <t>3934</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3329</t>
+          <t>3845</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>3359</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>102223</t>
+          <t>100048</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>121946</t>
+          <t>121403</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>68,43%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>114568</t>
+          <t>115281</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>134689</t>
+          <t>134442</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>72,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>222455</t>
+          <t>222532</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>252860</t>
+          <t>250585</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>61,06%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>68,78%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47102</t>
+          <t>47544</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>66759</t>
+          <t>67402</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>44165</t>
+          <t>43617</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>63725</t>
+          <t>63011</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>96742</t>
+          <t>97337</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>125146</t>
+          <t>124306</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,12%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4283</t>
+          <t>4489</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13735</t>
+          <t>14093</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>1939</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9133</t>
+          <t>9126</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7958</t>
+          <t>7962</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>19153</t>
+          <t>19658</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4492</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>614</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5447</t>
+          <t>5903</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1293</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7976</t>
+          <t>7616</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3757</t>
+          <t>3296</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>2657</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>170150</t>
+          <t>170576</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>196009</t>
+          <t>196528</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>67,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>190615</t>
+          <t>190652</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>218211</t>
+          <t>216814</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>70,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>370417</t>
+          <t>369016</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>406483</t>
+          <t>407370</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>61,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>67,95%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>79425</t>
+          <t>79514</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>105345</t>
+          <t>104771</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>78752</t>
+          <t>79270</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>105381</t>
+          <t>105305</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>166387</t>
+          <t>165532</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>200674</t>
+          <t>203662</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,97%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7375</t>
+          <t>6662</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18540</t>
+          <t>17557</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5905</t>
+          <t>5700</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15366</t>
+          <t>15742</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>15428</t>
+          <t>14748</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>29392</t>
+          <t>30268</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>642</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5625</t>
+          <t>6175</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>610</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5517</t>
+          <t>5667</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2111</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9322</t>
+          <t>9740</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4636</t>
+          <t>4630</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4364</t>
+          <t>4655</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse  alegre en 2012 (tasa de respuesta: 95,72%)</t>
+          <t>Menores según la frecuencia de sentirse alegre en 2012 (tasa de respuesta: 95,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>81108</t>
+          <t>79947</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>100195</t>
+          <t>100021</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>53,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>84858</t>
+          <t>84664</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>104954</t>
+          <t>105306</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>67,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>170148</t>
+          <t>171029</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>198113</t>
+          <t>199032</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>56,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>65,17%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41796</t>
+          <t>41987</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>60675</t>
+          <t>61190</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42587</t>
+          <t>40824</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>61644</t>
+          <t>60914</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>89862</t>
+          <t>90166</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>117696</t>
+          <t>116440</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,13%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2785</t>
+          <t>2639</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10807</t>
+          <t>10673</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3817</t>
+          <t>3878</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12577</t>
+          <t>12463</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8121</t>
+          <t>8551</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19811</t>
+          <t>19896</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>600</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6068</t>
+          <t>5436</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3611</t>
+          <t>3650</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>910</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6584</t>
+          <t>7550</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>3574</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4576</t>
+          <t>4542</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>587</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5547</t>
+          <t>5653</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>80936</t>
+          <t>81129</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>102947</t>
+          <t>102093</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>50,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>62,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>93143</t>
+          <t>93702</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>114315</t>
+          <t>114779</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>67,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>180986</t>
+          <t>180215</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>211071</t>
+          <t>210601</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>54,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>63,27%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54392</t>
+          <t>53007</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>75037</t>
+          <t>74390</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52901</t>
+          <t>52639</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>74224</t>
+          <t>73150</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>111059</t>
+          <t>112403</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>141103</t>
+          <t>142240</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>42,73%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1421</t>
+          <t>1530</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9092</t>
+          <t>9244</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>635</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6190</t>
+          <t>6106</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3687</t>
+          <t>3649</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12639</t>
+          <t>12853</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3063</t>
+          <t>4135</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3695</t>
+          <t>4293</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>578</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5525</t>
+          <t>5424</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5114</t>
+          <t>4475</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4458</t>
+          <t>4393</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>166874</t>
+          <t>167795</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>196520</t>
+          <t>195597</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>184999</t>
+          <t>184673</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>214121</t>
+          <t>213243</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>56,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>360633</t>
+          <t>360857</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>401399</t>
+          <t>399760</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>56,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>62,63%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>101589</t>
+          <t>102227</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>129609</t>
+          <t>129177</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>100156</t>
+          <t>100268</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>127306</t>
+          <t>127819</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>209276</t>
+          <t>209638</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>249816</t>
+          <t>248068</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>38,87%</t>
         </is>
       </c>
     </row>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5907</t>
+          <t>6158</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16892</t>
+          <t>16443</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5435</t>
+          <t>5514</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16218</t>
+          <t>15229</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>13806</t>
+          <t>14226</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>27886</t>
+          <t>27675</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -4711,12 +4711,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>680</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6874</t>
+          <t>7026</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4751,7 +4751,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5606</t>
+          <t>5468</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9523</t>
+          <t>9644</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>592</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5414</t>
+          <t>5710</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4775</t>
+          <t>4481</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8043</t>
+          <t>7781</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5089,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse  alegre en 2016 (tasa de respuesta: 95,77%)</t>
+          <t>Menores según la frecuencia de sentirse alegre en 2016 (tasa de respuesta: 95,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5284,12 +5284,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>103244</t>
+          <t>104471</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>125201</t>
+          <t>126254</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5299,12 +5299,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>69,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5319,12 +5319,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>102843</t>
+          <t>104657</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>125701</t>
+          <t>125535</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>70,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>213857</t>
+          <t>214436</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>244158</t>
+          <t>244784</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>68,09%</t>
         </is>
       </c>
     </row>
@@ -5397,12 +5397,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52049</t>
+          <t>51063</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>72450</t>
+          <t>72212</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5412,12 +5412,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5432,12 +5432,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48968</t>
+          <t>47695</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>70103</t>
+          <t>68304</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>106243</t>
+          <t>106821</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>135007</t>
+          <t>135610</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>37,72%</t>
         </is>
       </c>
     </row>
@@ -5510,12 +5510,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>1710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8834</t>
+          <t>8542</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>1226</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7287</t>
+          <t>7822</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4323</t>
+          <t>4064</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13766</t>
+          <t>12686</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3780</t>
+          <t>3057</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3530</t>
+          <t>3783</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2943</t>
+          <t>3877</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3680</t>
+          <t>3633</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>78939</t>
+          <t>78505</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>99481</t>
+          <t>100707</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>61,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>86077</t>
+          <t>83889</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>107108</t>
+          <t>106590</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>170360</t>
+          <t>172053</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>201232</t>
+          <t>202015</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>60,23%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>53263</t>
+          <t>52148</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>73053</t>
+          <t>74095</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>57199</t>
+          <t>57031</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>77808</t>
+          <t>79486</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>116361</t>
+          <t>116127</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>147682</t>
+          <t>145451</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>43,37%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6171</t>
+          <t>6097</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16535</t>
+          <t>17150</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2960</t>
+          <t>2906</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11139</t>
+          <t>11684</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>10345</t>
+          <t>10961</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>24011</t>
+          <t>24196</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -6310,7 +6310,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2669</t>
+          <t>2841</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6380,7 +6380,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2589</t>
+          <t>2913</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -6423,7 +6423,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3404</t>
+          <t>3814</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6458,7 +6458,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4140</t>
+          <t>4204</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6473,7 +6473,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6493,7 +6493,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4635</t>
+          <t>5730</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>190271</t>
+          <t>190265</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>220194</t>
+          <t>221744</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>195433</t>
+          <t>195551</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>228045</t>
+          <t>226418</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>56,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>397743</t>
+          <t>393387</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>438420</t>
+          <t>437515</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>56,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>62,96%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>109131</t>
+          <t>109274</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>139562</t>
+          <t>138798</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>110181</t>
+          <t>112032</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>141961</t>
+          <t>140237</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>230910</t>
+          <t>229674</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>270385</t>
+          <t>273356</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>39,34%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9637</t>
+          <t>9570</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>21850</t>
+          <t>22042</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5036</t>
+          <t>5244</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15565</t>
+          <t>15331</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>17358</t>
+          <t>17328</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>33692</t>
+          <t>34720</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -6992,7 +6992,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2776</t>
+          <t>2631</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7027,7 +7027,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>3803</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7062,7 +7062,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4449</t>
+          <t>4647</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7077,7 +7077,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -7105,7 +7105,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4534</t>
+          <t>3838</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7140,7 +7140,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4920</t>
+          <t>5919</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>724</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6052</t>
+          <t>5999</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7190,7 +7190,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP07C04-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07C04-Edad-trans_orig.xlsx
@@ -537,13 +537,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse alegre en 2007 (tasa de respuesta: 89,79%)</t>
+          <t>Menores según la frecuencia de sentirse alegre, percibida por el/la menor [KIDSCREEN 20] en 2007 (tasa de respuesta: 89,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>79443</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>70813</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>87526</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>64,34%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>57,35%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>70,88%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>108</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>72089</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>63082</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>79714</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>64098</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>80522</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>64,53%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>56,47%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>71,36%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>79443</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>70068</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>87665</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>64,34%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>72,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>139988</t>
+          <t>140992</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>163904</t>
+          <t>163390</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>59,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>69,47%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>38147</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>29167</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>46406</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>30,89%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>23,62%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>37,58%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>35041</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>27521</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>44013</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>27453</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>43793</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>31,37%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>24,64%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>39,4%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>38147</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>30470</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>47627</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>30,89%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>61950</t>
+          <t>62221</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>84146</t>
+          <t>84248</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,82%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5224</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2304</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9088</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>4,23%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1,87%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>7,36%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>3403</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1299</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>7999</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1290</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>7682</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>3,05%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>7,16%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>5224</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1923</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>9377</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>4,23%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4796</t>
+          <t>4682</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14271</t>
+          <t>14002</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -1061,107 +1061,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1178</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4030</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4115</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,05%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,61%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>3,68%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1178</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4086</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1178</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3934</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -1174,107 +1174,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3340</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2,71%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>667</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>3845</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>3329</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>3,11%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>3359</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -1287,57 +1287,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>123481</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>123481</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>123481</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>168</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>111711</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>111711</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>111711</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>123481</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>123481</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>123481</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>125574</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>114784</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>134981</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>67,48%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>61,68%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>72,53%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>111695</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>100048</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>121403</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>100319</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>122117</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>62,68%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>56,14%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>68,13%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>125574</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>115281</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>134442</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>67,48%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>56,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>222532</t>
+          <t>223085</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>250585</t>
+          <t>251320</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>61,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>68,99%</t>
         </is>
       </c>
     </row>
@@ -1517,72 +1517,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>53186</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>44467</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>63898</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>28,58%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>23,89%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>34,34%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>56956</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>47544</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>67402</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>46827</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>67871</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>31,96%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>26,68%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>37,82%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>53186</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>43617</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>63011</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>28,58%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>97337</t>
+          <t>96145</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>124306</t>
+          <t>123694</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>33,95%</t>
         </is>
       </c>
     </row>
@@ -1630,72 +1630,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>4583</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1981</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>8621</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>4,63%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>8267</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>4489</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>14093</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>4558</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>13763</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>4,64%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>7,91%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>4583</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>1939</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>9126</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7962</t>
+          <t>8369</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>19658</t>
+          <t>19599</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -1743,72 +1743,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2095</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5834</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,14%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1289</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3905</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4337</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,72%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2095</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>614</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5903</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,13%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7616</t>
+          <t>7650</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -1856,107 +1856,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>659</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3305</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>659</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3296</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>3551</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>659</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>2657</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -1969,57 +1969,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>186097</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>186097</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>186097</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>263</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>178206</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>178206</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>178206</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>186097</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>186097</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>186097</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2086,72 +2086,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>205018</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>190016</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>217178</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>66,22%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>61,38%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>70,15%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>183783</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>170576</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>196528</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>169690</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>196086</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>63,39%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>58,84%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>67,79%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>308</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>205018</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>190652</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>216814</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>66,22%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>58,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,04%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>369016</t>
+          <t>370382</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>407370</t>
+          <t>407239</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>61,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>67,93%</t>
         </is>
       </c>
     </row>
@@ -2204,67 +2204,67 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>91333</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>78848</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>104928</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>29,5%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>25,47%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>33,89%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
           <t>91996</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>79514</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>104771</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>80044</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>105687</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>31,73%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>27,43%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>36,14%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>91333</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>79270</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>105305</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>29,5%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>165532</t>
+          <t>165606</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>203662</t>
+          <t>201023</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>33,53%</t>
         </is>
       </c>
     </row>
@@ -2312,72 +2312,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>9807</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>5695</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>15145</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3,17%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>4,89%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>11669</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>6662</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>17557</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>7709</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>18638</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>4,03%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>2,3%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>6,06%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>9807</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>5700</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>15742</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>3,17%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>14748</t>
+          <t>15194</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>30268</t>
+          <t>29875</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -2425,72 +2425,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2095</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>676</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>6787</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>2467</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>6175</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>643</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>6324</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,85%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,22%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>2095</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>610</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>5667</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>1936</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9740</t>
+          <t>9045</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -2538,107 +2538,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1325</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>4655</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>1325</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>4630</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>4001</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>1325</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>4655</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -2651,57 +2651,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>466</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>309578</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>309578</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>309578</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>431</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>289916</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>289916</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>289916</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>466</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>309578</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>309578</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>309578</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2813,13 +2813,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse alegre en 2012 (tasa de respuesta: 95,72%)</t>
+          <t>Menores según la frecuencia de sentirse alegre, percibida por el/la menor [KIDSCREEN 20] en 2012 (tasa de respuesta: 95,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2830,7 +2830,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2998,72 +2998,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>94763</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>85585</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>104880</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>60,97%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>55,06%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>67,48%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>129</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>90159</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>79947</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>100021</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>80668</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>100153</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>60,12%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>53,31%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>66,7%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>94763</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>84664</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>105306</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>60,97%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>53,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>171029</t>
+          <t>170569</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>199032</t>
+          <t>199247</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,17%</t>
+          <t>65,24%</t>
         </is>
       </c>
     </row>
@@ -3116,67 +3116,67 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>51333</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>41443</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>61320</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>33,03%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>26,66%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>39,45%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>51267</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>41987</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>61190</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>41773</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>60734</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>34,19%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>28,0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>40,8%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>51333</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>40824</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>60914</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>33,03%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>90166</t>
+          <t>89309</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>116440</t>
+          <t>115855</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>37,94%</t>
         </is>
       </c>
     </row>
@@ -3224,72 +3224,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>7162</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3878</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>12709</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>4,61%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>8,18%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>5825</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2639</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>10673</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2836</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>10903</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>3,88%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>7,12%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>7162</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>3878</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>12463</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>4,61%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8551</t>
+          <t>8377</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19896</t>
+          <t>19484</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -3337,72 +3337,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>722</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3166</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>2120</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5436</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>596</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6350</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,41%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,4%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,62%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>722</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3650</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>723</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7550</t>
+          <t>6923</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -3450,72 +3450,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1448</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5144</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>3,31%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>594</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3574</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>2976</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,4%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,38%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1448</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>4542</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>592</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5653</t>
+          <t>5984</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -3563,57 +3563,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>155427</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>155427</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>155427</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>214</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>149965</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>149965</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>149965</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>155427</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>155427</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>155427</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3680,72 +3680,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>104068</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>92698</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>113765</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>60,98%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>54,32%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>66,67%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>130</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>92147</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>81129</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>102093</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>81028</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>102511</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>56,81%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>50,02%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>62,94%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>104068</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>93702</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>114779</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>60,98%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,91%</t>
+          <t>49,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>180215</t>
+          <t>180926</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>210601</t>
+          <t>211037</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>54,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>63,4%</t>
         </is>
       </c>
     </row>
@@ -3798,67 +3798,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>62686</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>53305</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>73064</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>36,73%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>31,24%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>42,82%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>63606</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>53007</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>74390</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>53881</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>73975</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>39,21%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>32,68%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>45,86%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>62686</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>52639</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>73150</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>36,73%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>112403</t>
+          <t>112188</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>142240</t>
+          <t>141486</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>42,51%</t>
         </is>
       </c>
     </row>
@@ -3906,72 +3906,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2694</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>724</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>6654</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>3,9%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>4380</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1530</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>9244</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>1609</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>9052</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>2,7%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>5,7%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>2694</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>635</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>6106</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3649</t>
+          <t>3521</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12853</t>
+          <t>12081</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -4019,72 +4019,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1204</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4191</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>678</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4135</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3890</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,42%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1204</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4293</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>577</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5424</t>
+          <t>5363</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -4132,107 +4132,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>1397</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4475</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>4681</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,86%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,76%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>2,89%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1397</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>4523</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1397</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>4393</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -4245,57 +4245,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>170651</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>170651</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>170651</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>162209</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>162209</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>162209</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>170651</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>170651</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>170651</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4362,72 +4362,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>198830</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>183698</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>213236</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>60,98%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>56,34%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>65,39%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>182306</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>167795</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>195597</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>167469</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>196246</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>58,4%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>53,75%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>62,66%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>291</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>198830</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>184673</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>213243</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>60,98%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>62,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>360857</t>
+          <t>362233</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>399760</t>
+          <t>401899</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>56,54%</t>
+          <t>56,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>62,97%</t>
         </is>
       </c>
     </row>
@@ -4480,67 +4480,67 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>114019</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>100933</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>129241</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>34,97%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>30,95%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>39,64%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
           <t>114874</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>102227</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>129177</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>102397</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>129373</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>36,8%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>32,75%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>41,38%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>114019</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>100268</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>127819</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>34,97%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>209638</t>
+          <t>210547</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>248068</t>
+          <t>248520</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>38,94%</t>
         </is>
       </c>
     </row>
@@ -4593,67 +4593,67 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>9856</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>5936</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>15665</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3,02%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
           <t>10205</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>6158</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>16443</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>5691</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>16267</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>3,27%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>1,97%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>5,27%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>9856</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>5514</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>15229</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>3,02%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>14226</t>
+          <t>13789</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>27675</t>
+          <t>28219</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -4701,72 +4701,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1925</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>5135</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>2798</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>7026</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>677</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>6948</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,9%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,22%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>1925</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>579</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>5468</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>2034</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9644</t>
+          <t>9439</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -4814,72 +4814,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1448</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>4738</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>1991</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>592</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>5710</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>595</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5119</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,64%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>1448</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>4481</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7781</t>
+          <t>7992</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -4927,57 +4927,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>474</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>326078</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>326078</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>326078</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>444</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>312174</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>312174</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>312174</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>474</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>326078</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>326078</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>326078</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5089,13 +5089,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse alegre en 2016 (tasa de respuesta: 95,77%)</t>
+          <t>Menores según la frecuencia de sentirse alegre, percibida por el/la menor [KIDSCREEN 20] en 2016 (tasa de respuesta: 95,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5106,7 +5106,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5274,72 +5274,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>115188</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>104201</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>125919</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>64,49%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>58,34%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>70,5%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>114852</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>104471</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>126254</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>104686</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>124628</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>63,49%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>57,75%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>69,8%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>115188</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>104657</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>125535</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>64,49%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>57,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>214436</t>
+          <t>215684</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>244784</t>
+          <t>245858</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>68,39%</t>
         </is>
       </c>
     </row>
@@ -5387,72 +5387,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>58539</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>47758</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>68703</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>32,77%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>26,74%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>38,47%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>61651</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>51063</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>72212</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>51965</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>72425</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>34,08%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>28,23%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>39,92%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>58539</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>47695</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>68304</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>32,77%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>106821</t>
+          <t>103896</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>135610</t>
+          <t>134858</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,51%</t>
         </is>
       </c>
     </row>
@@ -5500,74 +5500,74 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3398</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1289</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>7948</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,72%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>4,45%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>4384</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>8542</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1907</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>8537</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>2,42%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>4,72%</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>3398</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1226</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>7822</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>1,9%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>4,38%</t>
-        </is>
-      </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>12</t>
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4064</t>
+          <t>4391</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12686</t>
+          <t>12770</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -5613,107 +5613,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>759</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,14%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>759</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3057</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3794</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>759</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3783</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -5726,107 +5726,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>727</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4014</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>727</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>3877</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>4322</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>2,17%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>727</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>3633</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -5839,57 +5839,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>178611</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>178611</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>178611</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>180887</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>180887</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>180887</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>178611</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>178611</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>178611</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5961,67 +5961,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>96376</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>85552</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>107341</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>56,5%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>50,15%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>62,92%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>89884</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>78505</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>100707</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>79368</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>99950</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>54,54%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>47,63%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>61,11%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>96376</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>83889</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>106590</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>56,5%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>48,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>172053</t>
+          <t>170170</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>202015</t>
+          <t>200970</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>50,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>59,92%</t>
         </is>
       </c>
     </row>
@@ -6069,72 +6069,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>67504</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>56783</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>78809</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>39,57%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>33,29%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>46,2%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>63140</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>52148</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>74095</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>53600</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>74082</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>38,31%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>31,64%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>44,96%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>67504</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>57031</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>79486</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>39,57%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>116127</t>
+          <t>115172</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>145451</t>
+          <t>146002</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>43,53%</t>
         </is>
       </c>
     </row>
@@ -6182,72 +6182,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5948</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2751</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>11548</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>3,49%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>6,77%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>10500</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>6097</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>17150</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>6256</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>17539</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>6,37%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>3,7%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>10,41%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>5948</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>2906</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>11684</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>3,49%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>10961</t>
+          <t>10898</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>24196</t>
+          <t>24677</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,36%</t>
         </is>
       </c>
     </row>
@@ -6295,92 +6295,92 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>524</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2841</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>2633</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,32%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>524</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2913</t>
+          <t>2924</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6413,87 +6413,87 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>764</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3350</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1,96%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>759</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3814</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>4135</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,46%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,31%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>764</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>2,51%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1523</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>4204</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1523</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5730</t>
+          <t>5738</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6521,57 +6521,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>170592</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>170592</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>170592</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>164807</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>164807</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>164807</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>170592</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>170592</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>170592</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6638,72 +6638,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>211565</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>195841</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>226928</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>60,59%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>56,08%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>64,98%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>293</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>204736</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>190265</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>221744</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>189673</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>218491</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>59,22%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>55,04%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>64,14%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>211565</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>195551</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>226418</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>60,59%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>54,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>393387</t>
+          <t>393784</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>437515</t>
+          <t>438145</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>63,05%</t>
         </is>
       </c>
     </row>
@@ -6756,67 +6756,67 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>126042</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>111411</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>142860</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>36,09%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>31,9%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>40,91%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
           <t>124790</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>109274</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>138798</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>110504</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>139981</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>36,1%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>31,61%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>40,15%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>126042</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>112032</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>140237</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>36,09%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>229674</t>
+          <t>230702</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>273356</t>
+          <t>273375</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,7 +6846,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6864,72 +6864,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>9347</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>5570</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>16190</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2,68%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>4,64%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>14884</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>9570</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>22042</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>9751</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>22298</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>4,31%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>2,77%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>6,38%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>9347</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>5244</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>15331</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>2,68%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>17328</t>
+          <t>17809</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>34720</t>
+          <t>33515</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -6982,102 +6982,102 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>759</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>4278</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
           <t>524</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>2631</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>2628</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,15%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>0,76%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>759</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>1283</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>3803</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>4599</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1283</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>4647</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -7090,72 +7090,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1490</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>4628</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>759</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>3838</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>4269</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,22%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>1490</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>5919</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7175,7 +7175,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>6696</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7190,7 +7190,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -7203,57 +7203,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>349203</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>349203</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>349203</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>493</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>345694</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>345694</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>345694</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>349203</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>349203</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>349203</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
